--- a/data/output/parsed/Tech Mahindra_2017-18.xlsx
+++ b/data/output/parsed/Tech Mahindra_2017-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-15T21:36:18Z</t>
+          <t>2026-03-18T23:44:14Z</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-15T21:36:18Z</t>
+          <t>2026-03-18T23:44:14Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-15T21:36:18Z</t>
+          <t>2026-03-18T23:44:14Z</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-15T21:36:18Z</t>
+          <t>2026-03-18T23:44:14Z</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-15T21:36:18Z</t>
+          <t>2026-03-18T23:44:14Z</t>
         </is>
       </c>
     </row>

--- a/data/output/parsed/Tech Mahindra_2017-18.xlsx
+++ b/data/output/parsed/Tech Mahindra_2017-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-18T23:44:14Z</t>
+          <t>2026-03-19T20:46:22Z</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-18T23:44:14Z</t>
+          <t>2026-03-19T20:46:22Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-18T23:44:14Z</t>
+          <t>2026-03-19T20:46:22Z</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-18T23:44:14Z</t>
+          <t>2026-03-19T20:46:22Z</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-18T23:44:14Z</t>
+          <t>2026-03-19T20:46:22Z</t>
         </is>
       </c>
     </row>

--- a/data/output/parsed/Tech Mahindra_2017-18.xlsx
+++ b/data/output/parsed/Tech Mahindra_2017-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-19T20:46:22Z</t>
+          <t>2026-03-19T23:53:16Z</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-19T20:46:22Z</t>
+          <t>2026-03-19T23:53:16Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-19T20:46:22Z</t>
+          <t>2026-03-19T23:53:16Z</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-19T20:46:22Z</t>
+          <t>2026-03-19T23:53:16Z</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-19T20:46:22Z</t>
+          <t>2026-03-19T23:53:16Z</t>
         </is>
       </c>
     </row>

--- a/data/output/parsed/Tech Mahindra_2017-18.xlsx
+++ b/data/output/parsed/Tech Mahindra_2017-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-19T23:53:16Z</t>
+          <t>2026-03-20T04:23:56Z</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-19T23:53:16Z</t>
+          <t>2026-03-20T04:23:56Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-19T23:53:16Z</t>
+          <t>2026-03-20T04:23:56Z</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-19T23:53:16Z</t>
+          <t>2026-03-20T04:23:56Z</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-19T23:53:16Z</t>
+          <t>2026-03-20T04:23:56Z</t>
         </is>
       </c>
     </row>

--- a/data/output/parsed/Tech Mahindra_2017-18.xlsx
+++ b/data/output/parsed/Tech Mahindra_2017-18.xlsx
@@ -434,7 +434,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -476,7 +476,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>final_dividend_fy_2017_18</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:23:56Z</t>
+          <t>2026-03-21T01:02:31Z</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:23:56Z</t>
+          <t>2026-03-21T01:02:31Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:23:56Z</t>
+          <t>2026-03-21T01:02:31Z</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:23:56Z</t>
+          <t>2026-03-21T01:02:31Z</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:23:56Z</t>
+          <t>2026-03-21T01:02:31Z</t>
         </is>
       </c>
     </row>
